--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92567979043</v>
+        <v>46157.93097421667</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93097421667</v>
+        <v>46157.93172384023</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93172384023</v>
+        <v>46157.93399763882</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93399763882</v>
+        <v>46157.93717692632</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93717692632</v>
+        <v>46158.28216091969</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28216091969</v>
+        <v>46158.29680807979</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29680807979</v>
+        <v>46158.29814403273</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29814403273</v>
+        <v>46158.33387130866</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33387130866</v>
+        <v>46158.3685685155</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3685685155</v>
+        <v>46158.37287604373</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
